--- a/docs/Mapping_casi_uso/unioni_civili/Sciogl_UnCiv_004.xlsx
+++ b/docs/Mapping_casi_uso/unioni_civili/Sciogl_UnCiv_004.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="147">
   <si>
     <t>Sezione</t>
   </si>
@@ -396,6 +396,18 @@
   </si>
   <si>
     <t>evento.scioglimentoUnioneCivile.avvocatoConiuge2</t>
+  </si>
+  <si>
+    <t>Interprete</t>
+  </si>
+  <si>
+    <t>evento.interprete</t>
+  </si>
+  <si>
+    <t>evento.ausilioInterprete,!=,true &amp;&amp; evento.ausilioInterprete,!=,S &amp;&amp; evento.ausilioInterprete,!=,SI</t>
+  </si>
+  <si>
+    <t>Firmatario</t>
   </si>
   <si>
     <t>Dettagli evento</t>
@@ -499,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.31640625" customWidth="true" bestFit="true"/>
@@ -508,7 +520,7 @@
     <col min="4" max="4" width="49.76171875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="35.53515625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="62.171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="89.16796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2299,7 +2311,7 @@
         <v>109</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>18</v>
@@ -2322,7 +2334,7 @@
         <v>111</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>18</v>
@@ -2345,7 +2357,7 @@
         <v>113</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>18</v>
@@ -3920,22 +3932,22 @@
         <v>128</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D149" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="E149" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="150">
@@ -3943,22 +3955,22 @@
         <v>128</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
     </row>
     <row r="151">
@@ -3966,22 +3978,22 @@
         <v>128</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
     </row>
     <row r="152">
@@ -3989,22 +4001,22 @@
         <v>128</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153">
@@ -4012,22 +4024,22 @@
         <v>128</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>137</v>
+        <v>36</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
     </row>
     <row r="154">
@@ -4035,22 +4047,22 @@
         <v>128</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
     </row>
     <row r="155">
@@ -4058,21 +4070,619 @@
         <v>128</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D155" s="2" t="s">
+      <c r="C179" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E155" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G155" s="2" t="s">
+      <c r="E180" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="2" t="s">
         <v>18</v>
       </c>
     </row>
